--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.50_b0.10_x0.30_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.50_b0.10_x0.30_Q20_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02929289543463434</v>
+        <v>0.01564454802646215</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02929289543463434</v>
+        <v>0.01564454802646215</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02750596983702064</v>
+        <v>0.01453595027230284</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02750596983702064</v>
+        <v>0.01453595027230284</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02590810179041909</v>
+        <v>0.0135742950812762</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02590810179041909</v>
+        <v>0.0135742950812762</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02545543419026017</v>
+        <v>0.01332143269035222</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02545543419026017</v>
+        <v>0.01332143269035222</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02703265743063163</v>
+        <v>0.0142336070278174</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02703265743063163</v>
+        <v>0.0142336070278174</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03118480792575975</v>
+        <v>0.01657768252342769</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03118480792575975</v>
+        <v>0.01657768252342769</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03875874481396444</v>
+        <v>0.0207872870727723</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03875874481396444</v>
+        <v>0.0207872870727723</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04919941571299857</v>
+        <v>0.02653357605796468</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04919941571299857</v>
+        <v>0.02653357605796468</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0615199341622789</v>
+        <v>0.03323515470740569</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0615199341622789</v>
+        <v>0.03323515470740569</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.07483960750752838</v>
+        <v>0.0403756969161755</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07483960750752838</v>
+        <v>0.0403756969161755</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.08769904832155895</v>
+        <v>0.0471764791540859</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08769904832155895</v>
+        <v>0.0471764791540859</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1016989100197311</v>
+        <v>0.05457917507941865</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1016989100197311</v>
+        <v>0.05457917507941865</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1187582342679417</v>
+        <v>0.06370663688964251</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1187582342679417</v>
+        <v>0.06370663688964251</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.138049642987282</v>
+        <v>0.0741349045092705</v>
       </c>
       <c r="C15" t="n">
-        <v>0.138049642987282</v>
+        <v>0.0741349045092705</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1569910277895728</v>
+        <v>0.08442863504277015</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1569910277895728</v>
+        <v>0.08442863504277015</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1725625787814488</v>
+        <v>0.09291666390987685</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1725625787814488</v>
+        <v>0.09291666390987685</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1864740881461768</v>
+        <v>0.100475281465915</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1864740881461768</v>
+        <v>0.100475281465915</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1963498700996274</v>
+        <v>0.1058202243818601</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1963498700996274</v>
+        <v>0.1058202243818601</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2033381096472494</v>
+        <v>0.1095513957335763</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2033381096472494</v>
+        <v>0.1095513957335763</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2064923445129325</v>
+        <v>0.1111743799004366</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2064923445129325</v>
+        <v>0.1111743799004366</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2085316604750893</v>
+        <v>0.1121767466631136</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2085316604750893</v>
+        <v>0.1121767466631136</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.2061327646200214</v>
+        <v>0.1108057230659057</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2061327646200214</v>
+        <v>0.1108057230659057</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.2031738070789398</v>
+        <v>0.1091591046273578</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2031738070789398</v>
+        <v>0.1091591046273578</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1989571385526185</v>
+        <v>0.1068869742547634</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1989571385526185</v>
+        <v>0.1068869742547634</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1939164136704964</v>
+        <v>0.104201165890826</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1939164136704964</v>
+        <v>0.104201165890826</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1896034927803104</v>
+        <v>0.1018863684345358</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1896034927803104</v>
+        <v>0.1018863684345358</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1815191209601498</v>
+        <v>0.09758640268392518</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1815191209601498</v>
+        <v>0.09758640268392518</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1770221701070468</v>
+        <v>0.09519518523886009</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1770221701070468</v>
+        <v>0.09519518523886009</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1757328271125143</v>
+        <v>0.09454959099617331</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1757328271125143</v>
+        <v>0.09454959099617331</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1731933344106275</v>
+        <v>0.09320687913715867</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1731933344106275</v>
+        <v>0.09320687913715867</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
